--- a/#art_anonymized.xlsx
+++ b/#art_anonymized.xlsx
@@ -520,7 +520,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -691,7 +691,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4829,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4873,7 +4873,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -9996,7 +9996,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10122,7 +10122,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10206,7 +10206,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14659,7 +14659,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14701,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -14743,7 +14743,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19930,7 +19930,7 @@
       </c>
       <c r="J574" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -19975,7 +19975,7 @@
       </c>
       <c r="J575" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="J576" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20064,7 +20064,7 @@
       </c>
       <c r="J577" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="J578" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="J579" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="J580" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20240,7 +20240,7 @@
       </c>
       <c r="J581" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -20282,7 +20282,7 @@
       </c>
       <c r="J582" t="inlineStr">
         <is>
-          <t>中性</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
